--- a/daily_matches/job_matches_2026-05-01.xlsx
+++ b/daily_matches/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Developer - Senior - A&amp;I - Financial Services - Consulting - NYC, Charlotte, Dallas</t>
+          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, Redshift, BigQuery, Synapse, Docker</t>
+          <t>LangChain, RAG, LLaMA, Pinecone, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b189ba2f7b20d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Marketing Data Scientist</t>
+          <t>AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, NoSQL, Tableau, Power BI</t>
+          <t>Prompt Engineering, TensorFlow, PyTorch, Keras, S3, EC2, FastAPI, Docker, Kubernetes, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff7e89119e4b376</t>
+          <t>https://www.indeed.com/viewjob?jk=22f86c064f397503</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer Senior - Bay Area</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, Kafka, Hadoop, NoSQL, Power BI, Python, SQL</t>
+          <t>S3, Glue, Athena, Redshift, CI/CD, Redshift, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FSO Audit LABS - Kubernetes DevOps Engineer - Senior - Bay Area</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,29 +591,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>RAG, BigQuery, Apache Airflow, CI/CD, Terraform, Git, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7fd2619d1f1cba2</t>
+          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Consulting - Tech Consulting - FinTech - FSO, Blockchain and AI Engineering - Senior</t>
+          <t>Software Engineer III - Automation Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, AKS, Terraform, Git, R, Java, Scala</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d62863766448c8b</t>
+          <t>https://www.indeed.com/viewjob?jk=75ea03c43826f238</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FSO Audit LABS - Applications System Engineer - Senior - Bay Area</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, AKS, NoSQL, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Copilot, Kubernetes, PySpark, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0aff29719ea167</t>
+          <t>https://www.indeed.com/viewjob?jk=393bce2ff49f8f76</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>AI Engineer (LLM)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb4fb6963810c90</t>
+          <t>https://www.indeed.com/viewjob?jk=26f733e4569669b1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FinTech - AI Finance - Front-end Software Developer - Senior</t>
+          <t>Data Science Senior Associate - Card Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,52 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, AKS, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b5e9b7201bab03</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AI Data Science Summer Associate</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Tempus</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, XGBoost, Matplotlib, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a89c505e2b3887c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2bc679b5fdf632</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-01.xlsx
+++ b/daily_matches/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
+          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Pinecone, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, BigQuery, Docker, CI/CD, Jenkins, Git, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
+          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Platform Engineer</t>
+          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Manayunk, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Prompt Engineering, TensorFlow, PyTorch, Keras, S3, EC2, FastAPI, Docker, Kubernetes, Terraform</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, AWS SageMaker, AKS, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22f86c064f397503</t>
+          <t>https://www.indeed.com/viewjob?jk=7f7e3e3c0589ff3b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, Glue, Athena, Redshift, CI/CD, Redshift, Kafka, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
+          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, CI/CD, Terraform, Git, BigQuery, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, Keras, spaCy, NLTK, Redshift, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa04e033a8bfe1b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - Automation Engineering</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Data Lake, Git, Snowflake, Databricks, PySpark, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,112 +636,532 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75ea03c43826f238</t>
+          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Copilot, Kubernetes, PySpark, Python, R, Java, Scala</t>
+          <t>Data Lake, Git, Snowflake, Databricks, PySpark, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393bce2ff49f8f76</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer (LLM)</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Hugging Face, TensorFlow, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26f733e4569669b1</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb82821f25251e0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Science Senior Associate - Card Data &amp; Analytics</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, FastAPI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c780397359b6f81c</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DevOps/AI Ops Administrator</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Gemini, BigQuery, FastAPI, CI/CD, GitHub Actions, Git, BigQuery</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8d16d894b5774b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, LLaMA, Prompt Engineering, TensorFlow, PyTorch, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c049f920a5f229f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Azure Network Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Redshift, Synapse, CI/CD, GitHub Actions, Git, Redshift</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05c347498a9f2ed5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Platform Support Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Steifman LLP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, S3, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e7fe89c9128b371</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineer - Performance Management</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Lake Buena Vista, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1735188270c06e18</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Multi-Cloud Networking Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Java API Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2bc679b5fdf632</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Jenkins, Terraform, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c289c57d29e942cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Model Deployment Administrator</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, FastAPI, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a04c174e5bb55f00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI/ML Strategy Consultant</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, Docker, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f96b34606e52a6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI Model Deployment Administrator</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, FastAPI, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=301b8d10ac3cafae</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56cb9f10fe9e7a5a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-01.xlsx
+++ b/daily_matches/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
+          <t>Software Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, BigQuery, Docker, CI/CD, Jenkins, Git, BigQuery</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
+          <t>https://www.indeed.com/viewjob?jk=e8679bcf047d6c3e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior</t>
+          <t>AI Engineer/Data Scientist with Healthcare Payment Integrity Platform - Windsurf or GitHub Copilot or Cursor Experience</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Syncreon Consulting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Manayunk, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, AWS SageMaker, AKS, Snowflake</t>
+          <t>AI Engineer, Data Scientist, LLaMA, Gemini, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f7e3e3c0589ff3b</t>
+          <t>https://www.indeed.com/viewjob?jk=708ef42ee72ebd1f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior AI Specialist - SAP &amp; Industrial Integration</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, PostgreSQL, MySQL</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, XGBoost, Azure ML, Data Lake, MLflow, FastAPI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
+          <t>https://www.indeed.com/viewjob?jk=41281b6c560493fa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Backend Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, spaCy, NLTK, Redshift, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, Git, BigQuery, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa04e033a8bfe1b</t>
+          <t>https://www.indeed.com/viewjob?jk=2353cb4c2ecb06b9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Lake, Git, Snowflake, Databricks, PySpark, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
+          <t>https://www.indeed.com/viewjob?jk=19a23f9fb948e505</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plymouth, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Lake, Git, Snowflake, Databricks, PySpark, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>CI/CD, GitHub Actions, Terraform, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=84d603a90c06d3c1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>AI/ML Implementation Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Hugging Face, TensorFlow, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
+          <t>Data Scientist, RAG, Prompt Engineering, S3, FastAPI, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb82821f25251e0</t>
+          <t>https://www.indeed.com/viewjob?jk=837c2c0fee538b8f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Otomeshan technology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, FastAPI, CI/CD</t>
+          <t>Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,427 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c780397359b6f81c</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DevOps/AI Ops Administrator</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Gemini, BigQuery, FastAPI, CI/CD, GitHub Actions, Git, BigQuery</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d16d894b5774b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, LLaMA, Prompt Engineering, TensorFlow, PyTorch, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c049f920a5f229f</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Azure Network Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Redshift, Synapse, CI/CD, GitHub Actions, Git, Redshift</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=05c347498a9f2ed5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AI Platform Support Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Steifman LLP</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, S3, Git, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7fe89c9128b371</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Engineer - Performance Management</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>The Walt Disney Company</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Lake Buena Vista, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1735188270c06e18</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Multi-Cloud Networking Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Java API Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, Jenkins, Terraform, Git, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c289c57d29e942cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AI Model Deployment Administrator</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, FastAPI, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a04c174e5bb55f00</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AI/ML Strategy Consultant</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, Docker, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f96b34606e52a6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AI Model Deployment Administrator</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, FastAPI, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=301b8d10ac3cafae</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56cb9f10fe9e7a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=be5f68fc6ca68fb7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-01.xlsx
+++ b/daily_matches/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer - Sr. Consultant level</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, FastAPI, Docker, Kubernetes</t>
+          <t>Data Scientist, RAG, S3, Athena, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8679bcf047d6c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=98dbeaca2ef62c98</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer/Data Scientist with Healthcare Payment Integrity Platform - Windsurf or GitHub Copilot or Cursor Experience</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Syncreon Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LLaMA, Gemini, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
+          <t>Gemini, S3, EC2, Redshift, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=708ef42ee72ebd1f</t>
+          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Specialist - SAP &amp; Industrial Integration</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, XGBoost, Azure ML, Data Lake, MLflow, FastAPI</t>
+          <t>AI Engineer, Data Scientist, RAG, LLaMA, TensorFlow, PyTorch, EC2, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41281b6c560493fa</t>
+          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Remote, US)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, Git, BigQuery, Kafka, PostgreSQL, Python</t>
+          <t>TensorFlow, PyTorch, S3, Glue, Redshift, Data Lake, Kinesis, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2353cb4c2ecb06b9</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Edurech Technoogy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>TensorFlow, PyTorch, S3, Glue, Redshift, Data Lake, Kinesis, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a23f9fb948e505</t>
+          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plymouth, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CI/CD, GitHub Actions, Terraform, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, S3, Glue, Redshift, Data Lake, Kinesis, CI/CD, Terraform, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84d603a90c06d3c1</t>
+          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI/ML Implementation Engineer</t>
+          <t>Senior Full Stack Software Engineer (AI Applications)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Consumer Reports</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, S3, FastAPI, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, AWS SageMaker, FastAPI, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,917 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837c2c0fee538b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=c96afc5adffc5ff2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Senior Full Stack Software Engineer (AI Applications)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Otomeshan technology</t>
+          <t>Consumer Reports</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, AWS SageMaker, FastAPI, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=724bc484c5990c53</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer (AI Applications)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Consumer Reports</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, AWS SageMaker, FastAPI, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1acfb3f2cd34f77f</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer (AI Applications)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Consumer Reports</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, AWS SageMaker, FastAPI, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec355e4e62de03ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer (AI Applications)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Consumer Reports</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, AWS SageMaker, FastAPI, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2b6288dd8aefa12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AWS Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, FastAPI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b9534b4cb92adc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AWS Technical Apprentice / Trainee</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, FastAPI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2c0a53f632484cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 — Data Platform Enablement (Hybrid - Seattle, WA)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nordstrom</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=862af0113851f60e</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Junior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b71e56e3d482e1d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior SRE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Gemini, BigQuery, FastAPI, CI/CD, GitHub Actions, Git, BigQuery</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd467fdd92806914</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Azure AI Platform Engineer - Remote Role</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, Keras, spaCy, FastAPI, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e51b13499a8486c</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=505fbe53799f259a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AWS Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, FastAPI, Python, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=047af074cf3c1d18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AWS Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>S3, Kinesis, Docker, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c5b06678237c00c</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Cloud Migration Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Gemini, FastAPI, Docker, CI/CD, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AWS Technical Apprentice / Trainee</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, S3, EC2, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a20cc6812a2ccb13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SEACORP</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Middletown, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1665a0774a663eda</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Junior Cloud Networking Technician</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AWS Database Engineer / Cloud DBA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0dd996702bf636c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AWS API Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Databricks, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bf3d349d655acca</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Scientist - Innovation - PhD (Irving, TX)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Caris Life Sciences</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, PyTorch, S3, EC2, MLflow, Docker, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1925481add4e5a44</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Android</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Purple Wave Auction</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, GitHub Actions, Git, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43e1268f478abf6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AWS Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be5f68fc6ca68fb7</t>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8af5a18bee19fa8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AWS Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI NATIVE SOFTWARE ENGINEER</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BridgeNexus Technologies Inc</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97c9d3d43ea6b325</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c0c6ccf57790590</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, HBS AI Institute</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Harvard University</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, EC2, Git, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ccf10488804eb6ce</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-01.xlsx
+++ b/daily_matches/job_matches_2026-05-01.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>AI/ML Engineer - Work</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Athena, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow, Git</t>
+          <t>LangChain, LLaMA, Hugging Face, Pinecone, TensorFlow, PyTorch, AWS SageMaker, MLflow, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98dbeaca2ef62c98</t>
+          <t>https://www.indeed.com/viewjob?jk=e76fea76e5582b6f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gemini, S3, EC2, Redshift, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Snowflake</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccb9cb736f9f8e0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, LLaMA, TensorFlow, PyTorch, EC2, Docker, Kubernetes, AKS</t>
+          <t>Data Scientist, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AI Programmer (PT)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Somoza Law Firm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, S3, Glue, Redshift, Data Lake, Kinesis, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, Hadoop, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea16b2be0ccce5c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, S3, Glue, Redshift, Data Lake, Kinesis, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, LangChain, RAG, S3, Git, PostgreSQL, MySQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
+          <t>https://www.indeed.com/viewjob?jk=d6d36de223c163dc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Redshift, Data Lake, Kinesis, CI/CD, Terraform, Databricks</t>
+          <t>AI Engineer, LangChain, RAG, S3, Git, PostgreSQL, MySQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0f44c76ef0b75d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (AI Applications)</t>
+          <t>Senior Software Engineer (AI-First, Full-Stack, AWS, Kubernetes)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Consumer Reports</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, AWS SageMaker, FastAPI, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96afc5adffc5ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=54940ddff9a7d5fb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (AI Applications)</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Consumer Reports</t>
+          <t>USA Rare Earth LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, AWS SageMaker, FastAPI, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724bc484c5990c53</t>
+          <t>https://www.indeed.com/viewjob?jk=bb216c9527acdb42</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (AI Applications)</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Consumer Reports</t>
+          <t>USA Rare Earth LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, AWS SageMaker, FastAPI, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acfb3f2cd34f77f</t>
+          <t>https://www.indeed.com/viewjob?jk=d953f779bb28f2ff</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (AI Applications)</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Consumer Reports</t>
+          <t>USA Rare Earth LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, AWS SageMaker, FastAPI, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec355e4e62de03ae</t>
+          <t>https://www.indeed.com/viewjob?jk=21171bfd193ead06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (AI Applications)</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Consumer Reports</t>
+          <t>USA Rare Earth LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, AWS SageMaker, FastAPI, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2b6288dd8aefa12</t>
+          <t>https://www.indeed.com/viewjob?jk=10e8a6034c65395e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>USA Rare Earth LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, FastAPI, CI/CD</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9534b4cb92adc6</t>
+          <t>https://www.indeed.com/viewjob?jk=bf5a09410a87d4f8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>USA Rare Earth LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, FastAPI, CI/CD</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c0a53f632484cb</t>
+          <t>https://www.indeed.com/viewjob?jk=63d7600044d8c90f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer 2 — Data Platform Enablement (Hybrid - Seattle, WA)</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>USA Rare Earth LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862af0113851f60e</t>
+          <t>https://www.indeed.com/viewjob?jk=646d54e215c3182b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>USA Rare Earth LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b71e56e3d482e1d8</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4acc85900531f9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>USA Rare Earth LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, BigQuery, FastAPI, CI/CD, GitHub Actions, Git, BigQuery</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd467fdd92806914</t>
+          <t>https://www.indeed.com/viewjob?jk=59a88b1942d4081b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure AI Platform Engineer - Remote Role</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>USA Rare Earth LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, TensorFlow, PyTorch, Keras, spaCy, FastAPI, Kubernetes, Git, Python</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e51b13499a8486c</t>
+          <t>https://www.indeed.com/viewjob?jk=4ab98782c02fb74b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>USA Rare Earth LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=505fbe53799f259a</t>
+          <t>https://www.indeed.com/viewjob?jk=d079ecdec1afa4a7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>USA Rare Earth LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, FastAPI, Python, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047af074cf3c1d18</t>
+          <t>https://www.indeed.com/viewjob?jk=056bd38f29a9068e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>USA Rare Earth LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S3, Kinesis, Docker, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c5b06678237c00c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb7d064e3b107d07</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Computer Scientist / Software Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IS4S</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Auburn, AL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gemini, FastAPI, Docker, CI/CD, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
+          <t>https://www.indeed.com/viewjob?jk=599be15ceea4c365</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Computer Scientist / Software Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IS4S</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Aberdeen, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, S3, EC2, CI/CD, Python, R, Java, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a20cc6812a2ccb13</t>
+          <t>https://www.indeed.com/viewjob?jk=935977992fd944e4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>AI Automation Engineer, Finance &amp; Accounting</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SEACORP</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Middletown, RI, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python</t>
+          <t>AKS, Git, Snowflake, Databricks, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1665a0774a663eda</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc4b4b5640d9b20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Junior Cloud Networking Technician</t>
+          <t>Software Engineer QA II (Full Time) - United States</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
+          <t>https://www.indeed.com/viewjob?jk=afd590ce4a1068aa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Kafka, Python, R, Scala</t>
+          <t>RAG, Kubernetes, Terraform, MySQL, Cassandra, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dd996702bf636c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a3d15713be3da1af</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>AI Analyst - Finance Technology</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Victaulic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Databricks, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Cortex, Snowflake, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf3d349d655acca</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5b0af52c9a2689</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Scientist - Innovation - PhD (Irving, TX)</t>
+          <t>Software Engineer III - 3rd Party Multichannel Fulfillment</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, PyTorch, S3, EC2, MLflow, Docker, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1925481add4e5a44</t>
+          <t>https://www.indeed.com/viewjob?jk=5eee38c3b865dc21</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Android</t>
+          <t>Senior Application Security Engineer, AI and Machine Learning</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Purple Wave Auction</t>
+          <t>Lightning AI</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, GitHub Actions, Git, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e1268f478abf6c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3d02631645b78f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Senior Application Security Engineer, AI and Machine Learning</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lightning AI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, CI/CD, Python, R, Scala</t>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af5a18bee19fa8a</t>
+          <t>https://www.indeed.com/viewjob?jk=4349f9dbc7427f7e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>SAP NS2 Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ad87c768d1906393</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI NATIVE SOFTWARE ENGINEER</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Currency Technics and Metrics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Millersville, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>RAG, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c9d3d43ea6b325</t>
+          <t>https://www.indeed.com/viewjob?jk=603f016677295963</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Sales Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Power BI, Python, SQL, R</t>
+          <t>Generative AI, Copilot, Git, Snowflake, Databricks, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0c6ccf57790590</t>
+          <t>https://www.indeed.com/viewjob?jk=70a08962e8caa620</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccf10488804eb6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=0183c4d805b85a0a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-01.xlsx
+++ b/daily_matches/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Work</t>
+          <t>Senior Data Scientist-Data &amp; Personalization Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Rewards Network</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>City of Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, LLaMA, Hugging Face, Pinecone, TensorFlow, PyTorch, AWS SageMaker, MLflow, Docker, CI/CD</t>
+          <t>Data Scientist, Generative AI, RAG, AWS SageMaker, S3, Glue, Redshift, Kubernetes, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e76fea76e5582b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4582e40d2734ff3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Data Scientist-Intelligent Assignment Engine (Hybrid)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Rewards Network</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL</t>
+          <t>Data Scientist, Generative AI, RAG, AWS SageMaker, S3, Glue, Redshift, Kubernetes, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccb9cb736f9f8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=28f4e0d1d3bbb168</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Data Scientist-Intelligent Assignment Engine (Hybrid)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Rewards Network</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>City of Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, AWS SageMaker, S3, Glue, Redshift, Kubernetes, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
+          <t>https://www.indeed.com/viewjob?jk=e0c5d2be8683ada1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Programmer (PT)</t>
+          <t>Sr Associate Engineer/ Engineer, IT Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Somoza Law Firm</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, Hadoop, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Data Lake, FastAPI, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea16b2be0ccce5c</t>
+          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>#Software Engineer – Senior Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, S3, Git, PostgreSQL, MySQL, MongoDB, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6d36de223c163dc</t>
+          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, S3, Git, PostgreSQL, MySQL, MongoDB, SQL, R</t>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Apache Airflow, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0f44c76ef0b75d</t>
+          <t>https://www.indeed.com/viewjob?jk=ee86e3d398336334</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI-First, Full-Stack, AWS, Kubernetes)</t>
+          <t>Software Engineer III, Social</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Peloton</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>RAG, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54940ddff9a7d5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d1715e8569054151</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>USA Rare Earth LLC</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
+          <t>S3, Glue, Redshift, Data Lake, Apache Airflow, CI/CD, Databricks, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb216c9527acdb42</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Principle AI &amp; Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>USA Rare Earth LLC</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, MLflow, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d953f779bb28f2ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f42f8cc79a272b87</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>#Software Engineer – Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>USA Rare Earth LLC</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
+          <t>Copilot, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21171bfd193ead06</t>
+          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>USA Rare Earth LLC</t>
+          <t>Warehouse Specialists, LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, Git, Snowflake, PySpark, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e8a6034c65395e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9d4aee9428d96d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>USA Rare Earth LLC</t>
+          <t>Tillster</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
+          <t>RAG, Gemini, Prompt Engineering, Cortex, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf5a09410a87d4f8</t>
+          <t>https://www.indeed.com/viewjob?jk=e97e1c448ffd0875</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>USA Rare Earth LLC</t>
+          <t>Tillster</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
+          <t>RAG, Gemini, Prompt Engineering, Cortex, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d7600044d8c90f</t>
+          <t>https://www.indeed.com/viewjob?jk=913df1c4f4bba818</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>USA Rare Earth LLC</t>
+          <t>Tillster</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
+          <t>RAG, Gemini, Prompt Engineering, Cortex, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=646d54e215c3182b</t>
+          <t>https://www.indeed.com/viewjob?jk=41bbaf0ca103e268</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>USA Rare Earth LLC</t>
+          <t>Tillster</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
+          <t>RAG, Gemini, Prompt Engineering, Cortex, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4acc85900531f9</t>
+          <t>https://www.indeed.com/viewjob?jk=a14450a500edb34b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Senior Software Engineer – Edge AI/GenAI &amp; Multimedia</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>USA Rare Earth LLC</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
+          <t>LangChain, RAG, LLaMA, TensorFlow, PyTorch, Docker, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59a88b1942d4081b</t>
+          <t>https://www.indeed.com/viewjob?jk=5178d1310e5c11c7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Senior SDET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>USA Rare Earth LLC</t>
+          <t>CyberArk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ab98782c02fb74b</t>
+          <t>https://www.indeed.com/viewjob?jk=5322d19f930d0670</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Senior Software Engineer/Full Stack Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USA Rare Earth LLC</t>
+          <t>PTMA Financial Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
+          <t>RAG, Copilot, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d079ecdec1afa4a7</t>
+          <t>https://www.indeed.com/viewjob?jk=6f52cc39e10c279b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Senior Software Engineer/Full Stack Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USA Rare Earth LLC</t>
+          <t>PTMA Financial Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
+          <t>RAG, Copilot, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=056bd38f29a9068e</t>
+          <t>https://www.indeed.com/viewjob?jk=250528c29007ddb8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Sr SDET - Workplace Services Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USA Rare Earth LLC</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, ChromaDB, Git, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb7d064e3b107d07</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8b2a5bb6a25233</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Computer Scientist / Software Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IS4S</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Auburn, AL, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
+          <t>Jenkins, Git, Hadoop, MySQL, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599be15ceea4c365</t>
+          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Computer Scientist / Software Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IS4S</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Aberdeen, MD, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
+          <t>Generative AI, RAG, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=935977992fd944e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fff00f55ac4c10</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Automation Engineer, Finance &amp; Accounting</t>
+          <t>Software Developer 2 C# .NET Python, Azure AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Ivanti</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AKS, Git, Snowflake, Databricks, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, AKS, Terraform, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc4b4b5640d9b20</t>
+          <t>https://www.indeed.com/viewjob?jk=779142765ca7a9da</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer QA II (Full Time) - United States</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Southwest Airlines</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>RAG, S3, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd590ce4a1068aa</t>
+          <t>https://www.indeed.com/viewjob?jk=042c9624648e5202</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>AI Intern – Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>Oldcastle BuildingEnvelope</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Terraform, MySQL, Cassandra, Python, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, Git, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,287 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3d15713be3da1af</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AI Analyst - Finance Technology</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Victaulic</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>PA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Cortex, Snowflake, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5b0af52c9a2689</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Software Engineer III - 3rd Party Multichannel Fulfillment</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Wayfair</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5eee38c3b865dc21</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Application Security Engineer, AI and Machine Learning</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Lightning AI</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Hugging Face, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3d02631645b78f</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Application Security Engineer, AI and Machine Learning</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Lightning AI</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Hugging Face, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4349f9dbc7427f7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>SAP NS2 Senior DevSecOps Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad87c768d1906393</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Currency Technics and Metrics</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Millersville, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=603f016677295963</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Sales Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Precisely</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Generative AI, Copilot, Git, Snowflake, Databricks, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70a08962e8caa620</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist, HBS AI Institute</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Harvard University</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, S3, EC2, Git, Python, SQL, R, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0183c4d805b85a0a</t>
+          <t>https://www.indeed.com/viewjob?jk=b40d26fcbc5be7e2</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-01.xlsx
+++ b/daily_matches/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist-Data &amp; Personalization Platform (Hybrid)</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rewards Network</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>City of Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, AWS SageMaker, S3, Glue, Redshift, Kubernetes, Redshift, Kafka</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, BigQuery, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4582e40d2734ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist-Intelligent Assignment Engine (Hybrid)</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rewards Network</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, AWS SageMaker, S3, Glue, Redshift, Kubernetes, Redshift, Kafka</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, S3, EC2, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f4e0d1d3bbb168</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e4dd31abd9ea41</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist-Intelligent Assignment Engine (Hybrid)</t>
+          <t>Senior Professional Services Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rewards Network</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>City of Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, AWS SageMaker, S3, Glue, Redshift, Kubernetes, Redshift, Kafka</t>
+          <t>PyTorch, XGBoost, Azure ML, Redshift, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0c5d2be8683ada1</t>
+          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/ Engineer, IT Data</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, FastAPI, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake</t>
+          <t>AI Engineer, LangChain, RAG, Hugging Face, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>#Software Engineer – Senior Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, RAG, S3, EC2, Redshift, Data Lake, Git, Redshift, Hadoop, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Apache Airflow, CI/CD, Git, PostgreSQL</t>
+          <t>Generative AI, RAG, BigQuery, Kubernetes, Snowflake, BigQuery, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee86e3d398336334</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III, Social</t>
+          <t>Senior Data Engineer, Solutions Architecture</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Peloton</t>
+          <t>Clearway Energy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>Data Scientist, RAG, S3, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1715e8569054151</t>
+          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer, Solutions Architecture</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>Clearway Energy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, Data Lake, Apache Airflow, CI/CD, Databricks, Redshift, Python, SQL</t>
+          <t>Data Scientist, RAG, S3, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Principle AI &amp; Data Scientist</t>
+          <t>Senior Data Engineer, Solutions Architecture</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Clearway Energy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, MLflow, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, RAG, S3, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42f8cc79a272b87</t>
+          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>#Software Engineer – Engineer</t>
+          <t>Senior Software Engineer - FDE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copilot, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Docker, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
+          <t>https://www.indeed.com/viewjob?jk=6d423925d1d6a04f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Specialist - Data Sciences</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Warehouse Specialists, LLC</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Snowflake, PySpark, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, Docker, Kubernetes, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9d4aee9428d96d</t>
+          <t>https://www.indeed.com/viewjob?jk=19dfe85162d8b53a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tillster</t>
+          <t>USG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Cortex, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97e1c448ffd0875</t>
+          <t>https://www.indeed.com/viewjob?jk=18c268f18c608217</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tillster</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Cortex, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913df1c4f4bba818</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff12d0c32bc0655</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tillster</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Cortex, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41bbaf0ca103e268</t>
+          <t>https://www.indeed.com/viewjob?jk=25da12270e548fd3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tillster</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,69 +976,69 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Cortex, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14450a500edb34b</t>
+          <t>https://www.indeed.com/viewjob?jk=d901ce8e2d33bf0b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Edge AI/GenAI &amp; Multimedia</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, TensorFlow, PyTorch, Docker, Git, Python, R, Java</t>
+          <t>AI Engineer, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5178d1310e5c11c7</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0402bbb564aba1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior SDET</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CyberArk</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5322d19f930d0670</t>
+          <t>https://www.indeed.com/viewjob?jk=761d6dd774f8fb23</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer/Full Stack Developer</t>
+          <t>Senior Human Resources Decision Science Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PTMA Financial Solutions</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Cortex, Redshift, Snowflake, Databricks, Redshift, Tableau, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f52cc39e10c279b</t>
+          <t>https://www.indeed.com/viewjob?jk=b5b2490d4324be96</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer/Full Stack Developer</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PTMA Financial Solutions</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=250528c29007ddb8</t>
+          <t>https://www.indeed.com/viewjob?jk=f353e2ae3b0592ef</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr SDET - Workplace Services Engineering</t>
+          <t>AI Quality Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, MongoDB, SQL, R, Java</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8b2a5bb6a25233</t>
+          <t>https://www.indeed.com/viewjob?jk=e197af5ce9ad40f3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Platform Engineer, GenAI/ML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jenkins, Git, Hadoop, MySQL, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, MLflow, FastAPI, Snowflake, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9b449d7a7a9b0b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Florham Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fff00f55ac4c10</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6419d4b2dafe66</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Developer 2 C# .NET Python, Azure AI</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ivanti</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, AKS, Terraform, Python, SQL, R</t>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=779142765ca7a9da</t>
+          <t>https://www.indeed.com/viewjob?jk=d38c92fefcaa83ec</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>QA Engineer IV</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Southwest Airlines</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=042c9624648e5202</t>
+          <t>https://www.indeed.com/viewjob?jk=8fcef6fc1d987143</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Intern – Data, Analytics &amp; AI</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Oldcastle BuildingEnvelope</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Git, Power BI, Python, SQL, R</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,77 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b40d26fcbc5be7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=be99f12090d71cc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Merrimack, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fbe4d860faa09bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dev Ops Data Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>innoVet Health, LLC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Git, Databricks, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
         </is>
       </c>
     </row>
